--- a/raw/1956election.xlsx
+++ b/raw/1956election.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Dropbox/MyData/USvoting/historical voting/1920to1974/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE97F42-808E-8746-BEDD-D9134C46A78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EFC31A8-3D04-EC48-9615-750CC905CAED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="16300" windowHeight="15860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11851,7 +11851,7 @@
         <v>9</v>
       </c>
       <c r="D246">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="E246" t="s">
         <v>1495</v>
